--- a/Extractions/results_all_predictions.xlsx
+++ b/Extractions/results_all_predictions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I551"/>
+  <dimension ref="A1:J551"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,6 +474,11 @@
           <t>Predicted_MLP</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -505,6 +510,7 @@
       <c r="I2" t="n">
         <v>399.7665713601481</v>
       </c>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -536,6 +542,7 @@
       <c r="I3" t="n">
         <v>399.7665713601481</v>
       </c>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -567,6 +574,7 @@
       <c r="I4" t="n">
         <v>394.0218721237156</v>
       </c>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -598,6 +606,7 @@
       <c r="I5" t="n">
         <v>393.3872162273044</v>
       </c>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -629,6 +638,7 @@
       <c r="I6" t="n">
         <v>385.0475947265299</v>
       </c>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -660,6 +670,7 @@
       <c r="I7" t="n">
         <v>376.0107894640351</v>
       </c>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -691,6 +702,7 @@
       <c r="I8" t="n">
         <v>374.1890631346585</v>
       </c>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -722,6 +734,7 @@
       <c r="I9" t="n">
         <v>399.7665713601481</v>
       </c>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -753,6 +766,7 @@
       <c r="I10" t="n">
         <v>376.5468788714439</v>
       </c>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -784,6 +798,7 @@
       <c r="I11" t="n">
         <v>382.8064774704127</v>
       </c>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -815,6 +830,7 @@
       <c r="I12" t="n">
         <v>388.4092706107055</v>
       </c>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -846,6 +862,7 @@
       <c r="I13" t="n">
         <v>374.2541907357264</v>
       </c>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -877,6 +894,7 @@
       <c r="I14" t="n">
         <v>382.4329579277266</v>
       </c>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -908,6 +926,7 @@
       <c r="I15" t="n">
         <v>376.5468788714439</v>
       </c>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -933,12 +952,9 @@
       <c r="G16" t="n">
         <v>354</v>
       </c>
-      <c r="H16" t="n">
-        <v>432.2525849809771</v>
-      </c>
-      <c r="I16" t="n">
-        <v>484.6225096721978</v>
-      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -970,6 +986,7 @@
       <c r="I17" t="n">
         <v>374.5121988436083</v>
       </c>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1001,6 +1018,7 @@
       <c r="I18" t="n">
         <v>382.8064774704127</v>
       </c>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1032,6 +1050,7 @@
       <c r="I19" t="n">
         <v>374.2216269351924</v>
       </c>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1063,6 +1082,7 @@
       <c r="I20" t="n">
         <v>376.2788341677395</v>
       </c>
+      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1094,6 +1114,7 @@
       <c r="I21" t="n">
         <v>382.4329579277266</v>
       </c>
+      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1119,12 +1140,9 @@
       <c r="G22" t="n">
         <v>338</v>
       </c>
-      <c r="H22" t="n">
-        <v>433.9536656263066</v>
-      </c>
-      <c r="I22" t="n">
-        <v>489.8926074204533</v>
-      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1156,6 +1174,7 @@
       <c r="I23" t="n">
         <v>374.2541907357264</v>
       </c>
+      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1181,12 +1200,9 @@
       <c r="G24" t="n">
         <v>386</v>
       </c>
-      <c r="H24" t="n">
-        <v>326.3603148092122</v>
-      </c>
-      <c r="I24" t="n">
-        <v>404.5570522931016</v>
-      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1218,6 +1234,7 @@
       <c r="I25" t="n">
         <v>382.0594383850404</v>
       </c>
+      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1249,6 +1266,7 @@
       <c r="I26" t="n">
         <v>382.8064774704127</v>
       </c>
+      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1280,6 +1298,7 @@
       <c r="I27" t="n">
         <v>376.8301647874338</v>
       </c>
+      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1311,6 +1330,7 @@
       <c r="I28" t="n">
         <v>374.2216269351924</v>
       </c>
+      <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1336,11 +1356,12 @@
       <c r="G29" t="n">
         <v>365</v>
       </c>
-      <c r="H29" t="n">
-        <v>712.9308914603539</v>
-      </c>
-      <c r="I29" t="n">
-        <v>2168.082881651184</v>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Invalid</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -1373,6 +1394,7 @@
       <c r="I30" t="n">
         <v>383.179997013099</v>
       </c>
+      <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1404,6 +1426,7 @@
       <c r="I31" t="n">
         <v>390.8485926416592</v>
       </c>
+      <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1429,12 +1452,9 @@
       <c r="G32" t="n">
         <v>400</v>
       </c>
-      <c r="H32" t="n">
-        <v>338.6931494878515</v>
-      </c>
-      <c r="I32" t="n">
-        <v>385.7519436545431</v>
-      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1460,11 +1480,12 @@
       <c r="G33" t="n">
         <v>358</v>
       </c>
-      <c r="H33" t="n">
-        <v>508.8012140208072</v>
-      </c>
-      <c r="I33" t="n">
-        <v>846.8235592618927</v>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Invalid</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -1491,12 +1512,9 @@
       <c r="G34" t="n">
         <v>371</v>
       </c>
-      <c r="H34" t="n">
-        <v>289.3618107732944</v>
-      </c>
-      <c r="I34" t="n">
-        <v>501.2461754849106</v>
-      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1522,11 +1540,12 @@
       <c r="G35" t="n">
         <v>406</v>
       </c>
-      <c r="H35" t="n">
-        <v>501.1463511168241</v>
-      </c>
-      <c r="I35" t="n">
-        <v>799.8879318661832</v>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Invalid</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -1559,6 +1578,7 @@
       <c r="I36" t="n">
         <v>404.5222787104938</v>
       </c>
+      <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1584,11 +1604,12 @@
       <c r="G37" t="n">
         <v>390</v>
       </c>
-      <c r="H37" t="n">
-        <v>502.4221616008213</v>
-      </c>
-      <c r="I37" t="n">
-        <v>807.7105364321347</v>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Invalid</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -1621,6 +1642,7 @@
       <c r="I38" t="n">
         <v>414.0336934111852</v>
       </c>
+      <c r="J38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1646,11 +1668,12 @@
       <c r="G39" t="n">
         <v>389</v>
       </c>
-      <c r="H39" t="n">
-        <v>705.2760285563709</v>
-      </c>
-      <c r="I39" t="n">
-        <v>2117.805723610824</v>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Invalid</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -1683,6 +1706,7 @@
       <c r="I40" t="n">
         <v>388.4092706107055</v>
       </c>
+      <c r="J40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1714,6 +1738,7 @@
       <c r="I41" t="n">
         <v>374.2216269351924</v>
       </c>
+      <c r="J41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1739,11 +1764,12 @@
       <c r="G42" t="n">
         <v>417</v>
       </c>
-      <c r="H42" t="n">
-        <v>711.2298108150243</v>
-      </c>
-      <c r="I42" t="n">
-        <v>2156.910179864437</v>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Invalid</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -1776,6 +1802,7 @@
       <c r="I43" t="n">
         <v>411.6558397360124</v>
       </c>
+      <c r="J43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1807,6 +1834,7 @@
       <c r="I44" t="n">
         <v>414.8263113029094</v>
       </c>
+      <c r="J44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1832,11 +1860,12 @@
       <c r="G45" t="n">
         <v>382</v>
       </c>
-      <c r="H45" t="n">
-        <v>515.6055366021253</v>
-      </c>
-      <c r="I45" t="n">
-        <v>888.5441169469677</v>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Invalid</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -1869,6 +1898,7 @@
       <c r="I46" t="n">
         <v>401.3518071435967</v>
       </c>
+      <c r="J46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1900,6 +1930,7 @@
       <c r="I47" t="n">
         <v>374.7587033465532</v>
       </c>
+      <c r="J47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1925,11 +1956,12 @@
       <c r="G48" t="n">
         <v>385</v>
       </c>
-      <c r="H48" t="n">
-        <v>542.8228269273982</v>
-      </c>
-      <c r="I48" t="n">
-        <v>1056.970468853456</v>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Invalid</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -1962,6 +1994,7 @@
       <c r="I49" t="n">
         <v>388.4092706107055</v>
       </c>
+      <c r="J49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1987,12 +2020,9 @@
       <c r="G50" t="n">
         <v>392</v>
       </c>
-      <c r="H50" t="n">
-        <v>428.850423690318</v>
-      </c>
-      <c r="I50" t="n">
-        <v>474.0823141756869</v>
-      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2024,6 +2054,7 @@
       <c r="I51" t="n">
         <v>388.4092706107055</v>
       </c>
+      <c r="J51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2049,12 +2080,9 @@
       <c r="G52" t="n">
         <v>518</v>
       </c>
-      <c r="H52" t="n">
-        <v>434.0747215412068</v>
-      </c>
-      <c r="I52" t="n">
-        <v>534.7232563842934</v>
-      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2086,6 +2114,7 @@
       <c r="I53" t="n">
         <v>405.0652161902927</v>
       </c>
+      <c r="J53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2117,6 +2146,7 @@
       <c r="I54" t="n">
         <v>403.70274413957</v>
       </c>
+      <c r="J54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2148,6 +2178,7 @@
       <c r="I55" t="n">
         <v>393.4842037591498</v>
       </c>
+      <c r="J55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2179,6 +2210,7 @@
       <c r="I56" t="n">
         <v>394.1654397845111</v>
       </c>
+      <c r="J56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2210,6 +2242,7 @@
       <c r="I57" t="n">
         <v>376.0671194565065</v>
       </c>
+      <c r="J57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2241,6 +2274,7 @@
       <c r="I58" t="n">
         <v>415.7697897858706</v>
       </c>
+      <c r="J58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2272,6 +2306,7 @@
       <c r="I59" t="n">
         <v>391.4732273066421</v>
       </c>
+      <c r="J59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -2303,6 +2338,7 @@
       <c r="I60" t="n">
         <v>403.0215081142086</v>
       </c>
+      <c r="J60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -2334,6 +2370,7 @@
       <c r="I61" t="n">
         <v>392.1217317084272</v>
       </c>
+      <c r="J61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -2365,6 +2402,7 @@
       <c r="I62" t="n">
         <v>416.5175121106006</v>
       </c>
+      <c r="J62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -2396,6 +2434,7 @@
       <c r="I63" t="n">
         <v>403.70274413957</v>
       </c>
+      <c r="J63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -2421,11 +2460,12 @@
       <c r="G64" t="n">
         <v>464</v>
       </c>
-      <c r="H64" t="n">
-        <v>536.5648304223125</v>
-      </c>
-      <c r="I64" t="n">
-        <v>1206.702248769442</v>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Invalid</t>
+        </is>
       </c>
     </row>
     <row r="65">
@@ -2458,6 +2498,7 @@
       <c r="I65" t="n">
         <v>392.1217317084272</v>
       </c>
+      <c r="J65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -2489,6 +2530,7 @@
       <c r="I66" t="n">
         <v>415.7697897858706</v>
       </c>
+      <c r="J66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -2520,6 +2562,7 @@
       <c r="I67" t="n">
         <v>430.0832475916924</v>
       </c>
+      <c r="J67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -2551,6 +2594,7 @@
       <c r="I68" t="n">
         <v>392.1720956060504</v>
       </c>
+      <c r="J68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -2582,6 +2626,7 @@
       <c r="I69" t="n">
         <v>414.2743451364107</v>
       </c>
+      <c r="J69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -2613,6 +2658,7 @@
       <c r="I70" t="n">
         <v>402.3402720888473</v>
       </c>
+      <c r="J70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -2644,6 +2690,7 @@
       <c r="I71" t="n">
         <v>403.0215081142086</v>
       </c>
+      <c r="J71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -2675,6 +2722,7 @@
       <c r="I72" t="n">
         <v>403.0215081142086</v>
       </c>
+      <c r="J72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -2706,6 +2754,7 @@
       <c r="I73" t="n">
         <v>403.0215081142086</v>
       </c>
+      <c r="J73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -2737,6 +2786,7 @@
       <c r="I74" t="n">
         <v>403.0215081142086</v>
       </c>
+      <c r="J74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -2768,6 +2818,7 @@
       <c r="I75" t="n">
         <v>403.70274413957</v>
       </c>
+      <c r="J75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -2799,6 +2850,7 @@
       <c r="I76" t="n">
         <v>391.4732273066421</v>
       </c>
+      <c r="J76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -2830,6 +2882,7 @@
       <c r="I77" t="n">
         <v>403.0215081142086</v>
       </c>
+      <c r="J77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -2855,11 +2908,12 @@
       <c r="G78" t="n">
         <v>322</v>
       </c>
-      <c r="H78" t="n">
-        <v>587.5972497821992</v>
-      </c>
-      <c r="I78" t="n">
-        <v>1541.613831359633</v>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Invalid</t>
+        </is>
       </c>
     </row>
     <row r="79">
@@ -2892,6 +2946,7 @@
       <c r="I79" t="n">
         <v>402.3402720888473</v>
       </c>
+      <c r="J79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -2923,6 +2978,7 @@
       <c r="I80" t="n">
         <v>415.0220674611407</v>
       </c>
+      <c r="J80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -2954,6 +3010,7 @@
       <c r="I81" t="n">
         <v>384.6377926427848</v>
       </c>
+      <c r="J81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -2985,6 +3042,7 @@
       <c r="I82" t="n">
         <v>377.7072913135326</v>
       </c>
+      <c r="J82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -3016,6 +3074,7 @@
       <c r="I83" t="n">
         <v>392.8029677337885</v>
       </c>
+      <c r="J83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -3047,6 +3106,7 @@
       <c r="I84" t="n">
         <v>403.70274413957</v>
       </c>
+      <c r="J84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -3078,6 +3138,7 @@
       <c r="I85" t="n">
         <v>403.0215081142086</v>
       </c>
+      <c r="J85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -3109,6 +3170,7 @@
       <c r="I86" t="n">
         <v>403.0215081142086</v>
       </c>
+      <c r="J86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -3140,6 +3202,7 @@
       <c r="I87" t="n">
         <v>403.0215081142086</v>
       </c>
+      <c r="J87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -3171,6 +3234,7 @@
       <c r="I88" t="n">
         <v>415.0220674611407</v>
       </c>
+      <c r="J88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -3202,6 +3266,7 @@
       <c r="I89" t="n">
         <v>403.0215081142086</v>
       </c>
+      <c r="J89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -3233,6 +3298,7 @@
       <c r="I90" t="n">
         <v>428.0858811575557</v>
       </c>
+      <c r="J90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -3264,6 +3330,7 @@
       <c r="I91" t="n">
         <v>403.0215081142086</v>
       </c>
+      <c r="J91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -3295,6 +3362,7 @@
       <c r="I92" t="n">
         <v>391.4732273066421</v>
       </c>
+      <c r="J92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -3326,6 +3394,7 @@
       <c r="I93" t="n">
         <v>413.5266228116807</v>
       </c>
+      <c r="J93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -3357,6 +3426,7 @@
       <c r="I94" t="n">
         <v>414.2743451364107</v>
       </c>
+      <c r="J94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -3388,6 +3458,7 @@
       <c r="I95" t="n">
         <v>391.4732273066421</v>
       </c>
+      <c r="J95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -3419,6 +3490,7 @@
       <c r="I96" t="n">
         <v>403.0215081142086</v>
       </c>
+      <c r="J96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -3450,6 +3522,7 @@
       <c r="I97" t="n">
         <v>402.3402720888473</v>
       </c>
+      <c r="J97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -3481,6 +3554,7 @@
       <c r="I98" t="n">
         <v>403.0215081142086</v>
       </c>
+      <c r="J98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -3512,6 +3586,7 @@
       <c r="I99" t="n">
         <v>415.7697897858706</v>
       </c>
+      <c r="J99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -3543,6 +3618,7 @@
       <c r="I100" t="n">
         <v>413.5266228116807</v>
       </c>
+      <c r="J100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -3568,11 +3644,12 @@
       <c r="G101" t="n">
         <v>408</v>
       </c>
-      <c r="H101" t="n">
-        <v>560.3799594569264</v>
-      </c>
-      <c r="I101" t="n">
-        <v>1362.994320644865</v>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Invalid</t>
+        </is>
       </c>
     </row>
     <row r="102">
@@ -3605,6 +3682,7 @@
       <c r="I102" t="n">
         <v>403.0215081142086</v>
       </c>
+      <c r="J102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -3636,6 +3714,7 @@
       <c r="I103" t="n">
         <v>402.3402720888473</v>
       </c>
+      <c r="J103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -3667,6 +3746,7 @@
       <c r="I104" t="n">
         <v>384.6377926427848</v>
       </c>
+      <c r="J104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -3698,6 +3778,7 @@
       <c r="I105" t="n">
         <v>398.2528559366793</v>
       </c>
+      <c r="J105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -3729,6 +3810,7 @@
       <c r="I106" t="n">
         <v>403.0215081142086</v>
       </c>
+      <c r="J106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -3760,6 +3842,7 @@
       <c r="I107" t="n">
         <v>416.5175121106006</v>
       </c>
+      <c r="J107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -3791,6 +3874,7 @@
       <c r="I108" t="n">
         <v>378.4212968587335</v>
       </c>
+      <c r="J108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -3822,6 +3906,7 @@
       <c r="I109" t="n">
         <v>392.8029677337885</v>
       </c>
+      <c r="J109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -3853,6 +3938,7 @@
       <c r="I110" t="n">
         <v>392.8029677337885</v>
       </c>
+      <c r="J110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -3884,6 +3970,7 @@
       <c r="I111" t="n">
         <v>392.8029677337885</v>
       </c>
+      <c r="J111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -3915,6 +4002,7 @@
       <c r="I112" t="n">
         <v>404.3839801649313</v>
       </c>
+      <c r="J112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -3946,6 +4034,7 @@
       <c r="I113" t="n">
         <v>393.4842037591498</v>
       </c>
+      <c r="J113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -3977,6 +4066,7 @@
       <c r="I114" t="n">
         <v>404.3839801649313</v>
       </c>
+      <c r="J114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -4008,6 +4098,7 @@
       <c r="I115" t="n">
         <v>403.70274413957</v>
       </c>
+      <c r="J115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -4039,6 +4130,7 @@
       <c r="I116" t="n">
         <v>392.1217317084272</v>
       </c>
+      <c r="J116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -4070,6 +4162,7 @@
       <c r="I117" t="n">
         <v>402.3402720888473</v>
       </c>
+      <c r="J117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -4101,6 +4194,7 @@
       <c r="I118" t="n">
         <v>403.70274413957</v>
       </c>
+      <c r="J118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -4132,6 +4226,7 @@
       <c r="I119" t="n">
         <v>414.2743451364107</v>
       </c>
+      <c r="J119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -4163,6 +4258,7 @@
       <c r="I120" t="n">
         <v>392.8029677337885</v>
       </c>
+      <c r="J120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -4194,6 +4290,7 @@
       <c r="I121" t="n">
         <v>403.70274413957</v>
       </c>
+      <c r="J121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -4219,12 +4316,9 @@
       <c r="G122" t="n">
         <v>441</v>
       </c>
-      <c r="H122" t="n">
-        <v>511.4738909037015</v>
-      </c>
-      <c r="I122" t="n">
-        <v>1042.037387329265</v>
-      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -4256,6 +4350,7 @@
       <c r="I123" t="n">
         <v>374.4523343434296</v>
       </c>
+      <c r="J123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -4287,6 +4382,7 @@
       <c r="I124" t="n">
         <v>373.200215978302</v>
       </c>
+      <c r="J124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -4318,6 +4414,7 @@
       <c r="I125" t="n">
         <v>374.4523343434296</v>
       </c>
+      <c r="J125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -4349,6 +4446,7 @@
       <c r="I126" t="n">
         <v>377.1316068980532</v>
       </c>
+      <c r="J126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -4380,6 +4478,7 @@
       <c r="I127" t="n">
         <v>419.2526521221886</v>
       </c>
+      <c r="J127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -4411,6 +4510,7 @@
       <c r="I128" t="n">
         <v>423.1169737636342</v>
       </c>
+      <c r="J128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -4436,12 +4536,9 @@
       <c r="G129" t="n">
         <v>399</v>
       </c>
-      <c r="H129" t="n">
-        <v>476.5444910446241</v>
-      </c>
-      <c r="I129" t="n">
-        <v>472.2814356122923</v>
-      </c>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -4467,11 +4564,12 @@
       <c r="G130" t="n">
         <v>357</v>
       </c>
-      <c r="H130" t="n">
-        <v>288.5750797357081</v>
-      </c>
-      <c r="I130" t="n">
-        <v>544.7341884459239</v>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Invalid</t>
+        </is>
       </c>
     </row>
     <row r="131">
@@ -4504,6 +4602,7 @@
       <c r="I131" t="n">
         <v>419.1787376223751</v>
       </c>
+      <c r="J131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -4535,6 +4634,7 @@
       <c r="I132" t="n">
         <v>419.3265666220022</v>
       </c>
+      <c r="J132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -4566,6 +4666,7 @@
       <c r="I133" t="n">
         <v>415.698136384819</v>
       </c>
+      <c r="J133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -4591,12 +4692,9 @@
       <c r="G134" t="n">
         <v>458</v>
       </c>
-      <c r="H134" t="n">
-        <v>492.7047571752548</v>
-      </c>
-      <c r="I134" t="n">
-        <v>504.8545432897813</v>
-      </c>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -4628,6 +4726,7 @@
       <c r="I135" t="n">
         <v>416.6656446287121</v>
       </c>
+      <c r="J135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -4653,11 +4752,12 @@
       <c r="G136" t="n">
         <v>447</v>
       </c>
-      <c r="H136" t="n">
-        <v>274.9664345730716</v>
-      </c>
-      <c r="I136" t="n">
-        <v>572.649271119133</v>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>Invalid</t>
+        </is>
       </c>
     </row>
     <row r="137">
@@ -4690,6 +4790,7 @@
       <c r="I137" t="n">
         <v>417.9961056253572</v>
       </c>
+      <c r="J137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -4721,6 +4822,7 @@
       <c r="I138" t="n">
         <v>431.4804705685983</v>
       </c>
+      <c r="J138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -4752,6 +4854,7 @@
       <c r="I139" t="n">
         <v>426.1881909970259</v>
       </c>
+      <c r="J139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -4777,12 +4880,9 @@
       <c r="G140" t="n">
         <v>464</v>
       </c>
-      <c r="H140" t="n">
-        <v>478.2455716899536</v>
-      </c>
-      <c r="I140" t="n">
-        <v>475.6196509194651</v>
-      </c>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -4814,6 +4914,7 @@
       <c r="I141" t="n">
         <v>405.0652161902927</v>
       </c>
+      <c r="J141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -4845,6 +4946,7 @@
       <c r="I142" t="n">
         <v>388.5829328868485</v>
       </c>
+      <c r="J142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -4876,6 +4978,7 @@
       <c r="I143" t="n">
         <v>404.3839801649313</v>
       </c>
+      <c r="J143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -4907,6 +5010,7 @@
       <c r="I144" t="n">
         <v>392.1217317084272</v>
       </c>
+      <c r="J144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -4938,6 +5042,7 @@
       <c r="I145" t="n">
         <v>393.4842037591498</v>
       </c>
+      <c r="J145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -4969,6 +5074,7 @@
       <c r="I146" t="n">
         <v>403.70274413957</v>
       </c>
+      <c r="J146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -5000,6 +5106,7 @@
       <c r="I147" t="n">
         <v>402.3402720888473</v>
       </c>
+      <c r="J147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -5031,6 +5138,7 @@
       <c r="I148" t="n">
         <v>405.0652161902927</v>
       </c>
+      <c r="J148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -5062,6 +5170,7 @@
       <c r="I149" t="n">
         <v>392.1217317084272</v>
       </c>
+      <c r="J149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -5093,6 +5202,7 @@
       <c r="I150" t="n">
         <v>393.4842037591498</v>
       </c>
+      <c r="J150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -5124,6 +5234,7 @@
       <c r="I151" t="n">
         <v>394.1654397845111</v>
       </c>
+      <c r="J151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -5155,6 +5266,7 @@
       <c r="I152" t="n">
         <v>403.70274413957</v>
       </c>
+      <c r="J152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -5186,6 +5298,7 @@
       <c r="I153" t="n">
         <v>403.70274413957</v>
       </c>
+      <c r="J153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -5217,6 +5330,7 @@
       <c r="I154" t="n">
         <v>392.8029677337885</v>
       </c>
+      <c r="J154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -5248,6 +5362,7 @@
       <c r="I155" t="n">
         <v>403.70274413957</v>
       </c>
+      <c r="J155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -5279,6 +5394,7 @@
       <c r="I156" t="n">
         <v>384.6377926427848</v>
       </c>
+      <c r="J156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -5310,6 +5426,7 @@
       <c r="I157" t="n">
         <v>403.70274413957</v>
       </c>
+      <c r="J157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -5341,6 +5458,7 @@
       <c r="I158" t="n">
         <v>391.4732273066421</v>
       </c>
+      <c r="J158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -5372,6 +5490,7 @@
       <c r="I159" t="n">
         <v>391.4732273066421</v>
       </c>
+      <c r="J159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -5403,6 +5522,7 @@
       <c r="I160" t="n">
         <v>384.6377926427848</v>
       </c>
+      <c r="J160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -5434,6 +5554,7 @@
       <c r="I161" t="n">
         <v>392.8029677337885</v>
       </c>
+      <c r="J161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -5465,6 +5586,7 @@
       <c r="I162" t="n">
         <v>394.1654397845111</v>
       </c>
+      <c r="J162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -5496,6 +5618,7 @@
       <c r="I163" t="n">
         <v>378.064294086133</v>
       </c>
+      <c r="J163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -5527,6 +5650,7 @@
       <c r="I164" t="n">
         <v>400.9778000381246</v>
       </c>
+      <c r="J164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -5558,6 +5682,7 @@
       <c r="I165" t="n">
         <v>404.3839801649313</v>
       </c>
+      <c r="J165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -5589,6 +5714,7 @@
       <c r="I166" t="n">
         <v>392.8029677337885</v>
       </c>
+      <c r="J166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -5620,6 +5746,7 @@
       <c r="I167" t="n">
         <v>378.064294086133</v>
       </c>
+      <c r="J167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -5651,6 +5778,7 @@
       <c r="I168" t="n">
         <v>378.4212968587335</v>
       </c>
+      <c r="J168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -5682,6 +5810,7 @@
       <c r="I169" t="n">
         <v>392.8029677337885</v>
       </c>
+      <c r="J169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -5713,6 +5842,7 @@
       <c r="I170" t="n">
         <v>385.0685374467042</v>
       </c>
+      <c r="J170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -5744,6 +5874,7 @@
       <c r="I171" t="n">
         <v>403.70274413957</v>
       </c>
+      <c r="J171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -5775,6 +5906,7 @@
       <c r="I172" t="n">
         <v>384.6377926427848</v>
       </c>
+      <c r="J172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -5806,6 +5938,7 @@
       <c r="I173" t="n">
         <v>392.8029677337885</v>
       </c>
+      <c r="J173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -5837,6 +5970,7 @@
       <c r="I174" t="n">
         <v>378.4212968587335</v>
       </c>
+      <c r="J174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -5868,6 +6002,7 @@
       <c r="I175" t="n">
         <v>392.8029677337885</v>
       </c>
+      <c r="J175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -5899,6 +6034,7 @@
       <c r="I176" t="n">
         <v>378.064294086133</v>
       </c>
+      <c r="J176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -5930,6 +6066,7 @@
       <c r="I177" t="n">
         <v>384.6377926427848</v>
       </c>
+      <c r="J177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -5961,6 +6098,7 @@
       <c r="I178" t="n">
         <v>376.031517411683</v>
       </c>
+      <c r="J178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -5992,6 +6130,7 @@
       <c r="I179" t="n">
         <v>384.2070478388654</v>
       </c>
+      <c r="J179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -6023,6 +6162,7 @@
       <c r="I180" t="n">
         <v>378.7782996313338</v>
       </c>
+      <c r="J180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -6054,6 +6194,7 @@
       <c r="I181" t="n">
         <v>384.6377926427848</v>
       </c>
+      <c r="J181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -6085,6 +6226,7 @@
       <c r="I182" t="n">
         <v>391.4732273066421</v>
       </c>
+      <c r="J182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -6116,6 +6258,7 @@
       <c r="I183" t="n">
         <v>383.7763030349461</v>
       </c>
+      <c r="J183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -6147,6 +6290,7 @@
       <c r="I184" t="n">
         <v>384.6377926427848</v>
       </c>
+      <c r="J184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -6178,6 +6322,7 @@
       <c r="I185" t="n">
         <v>384.2070478388654</v>
       </c>
+      <c r="J185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -6209,6 +6354,7 @@
       <c r="I186" t="n">
         <v>391.4732273066421</v>
       </c>
+      <c r="J186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -6240,6 +6386,7 @@
       <c r="I187" t="n">
         <v>392.1217317084272</v>
       </c>
+      <c r="J187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -6271,6 +6418,7 @@
       <c r="I188" t="n">
         <v>384.6377926427848</v>
       </c>
+      <c r="J188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -6302,6 +6450,7 @@
       <c r="I189" t="n">
         <v>377.7072913135326</v>
       </c>
+      <c r="J189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -6333,6 +6482,7 @@
       <c r="I190" t="n">
         <v>376.0671194565065</v>
       </c>
+      <c r="J190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -6364,6 +6514,7 @@
       <c r="I191" t="n">
         <v>384.2070478388654</v>
       </c>
+      <c r="J191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -6395,6 +6546,7 @@
       <c r="I192" t="n">
         <v>389.546364360113</v>
       </c>
+      <c r="J192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -6426,6 +6578,7 @@
       <c r="I193" t="n">
         <v>384.6377926427848</v>
       </c>
+      <c r="J193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -6457,6 +6610,7 @@
       <c r="I194" t="n">
         <v>387.6530062702203</v>
       </c>
+      <c r="J194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -6488,6 +6642,7 @@
       <c r="I195" t="n">
         <v>384.2070478388654</v>
       </c>
+      <c r="J195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -6519,6 +6674,7 @@
       <c r="I196" t="n">
         <v>384.6377926427848</v>
       </c>
+      <c r="J196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -6550,6 +6706,7 @@
       <c r="I197" t="n">
         <v>383.7763030349461</v>
       </c>
+      <c r="J197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -6581,6 +6738,7 @@
       <c r="I198" t="n">
         <v>384.2070478388654</v>
       </c>
+      <c r="J198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -6612,6 +6770,7 @@
       <c r="I199" t="n">
         <v>376.2778754976271</v>
       </c>
+      <c r="J199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -6643,6 +6802,7 @@
       <c r="I200" t="n">
         <v>403.0215081142086</v>
       </c>
+      <c r="J200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -6674,6 +6834,7 @@
       <c r="I201" t="n">
         <v>384.2070478388654</v>
       </c>
+      <c r="J201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -6705,6 +6866,7 @@
       <c r="I202" t="n">
         <v>391.4732273066421</v>
       </c>
+      <c r="J202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -6736,6 +6898,7 @@
       <c r="I203" t="n">
         <v>384.2070478388654</v>
       </c>
+      <c r="J203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -6767,6 +6930,7 @@
       <c r="I204" t="n">
         <v>378.064294086133</v>
       </c>
+      <c r="J204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -6798,6 +6962,7 @@
       <c r="I205" t="n">
         <v>377.7072913135326</v>
       </c>
+      <c r="J205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -6829,6 +6994,7 @@
       <c r="I206" t="n">
         <v>384.6377926427848</v>
       </c>
+      <c r="J206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -6860,6 +7026,7 @@
       <c r="I207" t="n">
         <v>384.2070478388654</v>
       </c>
+      <c r="J207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -6891,6 +7058,7 @@
       <c r="I208" t="n">
         <v>377.3502885409321</v>
       </c>
+      <c r="J208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -6922,6 +7090,7 @@
       <c r="I209" t="n">
         <v>377.7072913135326</v>
       </c>
+      <c r="J209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -6953,6 +7122,7 @@
       <c r="I210" t="n">
         <v>391.4732273066421</v>
       </c>
+      <c r="J210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -6984,6 +7154,7 @@
       <c r="I211" t="n">
         <v>402.3402720888473</v>
       </c>
+      <c r="J211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -7015,6 +7186,7 @@
       <c r="I212" t="n">
         <v>377.0015368633445</v>
       </c>
+      <c r="J212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -7046,6 +7218,7 @@
       <c r="I213" t="n">
         <v>383.3455582310268</v>
       </c>
+      <c r="J213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -7077,6 +7250,7 @@
       <c r="I214" t="n">
         <v>384.2070478388654</v>
       </c>
+      <c r="J214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -7108,6 +7282,7 @@
       <c r="I215" t="n">
         <v>392.1217317084272</v>
       </c>
+      <c r="J215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -7139,6 +7314,7 @@
       <c r="I216" t="n">
         <v>377.3502885409321</v>
       </c>
+      <c r="J216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -7170,6 +7346,7 @@
       <c r="I217" t="n">
         <v>383.0122541276269</v>
       </c>
+      <c r="J217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -7201,6 +7378,7 @@
       <c r="I218" t="n">
         <v>393.0334756174935</v>
       </c>
+      <c r="J218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -7230,8 +7408,9 @@
         <v>387.7202739559764</v>
       </c>
       <c r="I219" t="n">
-        <v>387.6530062702203</v>
-      </c>
+        <v>387.6530062702201</v>
+      </c>
+      <c r="J219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -7263,6 +7442,7 @@
       <c r="I220" t="n">
         <v>377.7072913135326</v>
       </c>
+      <c r="J220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -7294,6 +7474,7 @@
       <c r="I221" t="n">
         <v>383.7763030349461</v>
       </c>
+      <c r="J221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -7325,6 +7506,7 @@
       <c r="I222" t="n">
         <v>390.9915115700099</v>
       </c>
+      <c r="J222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -7356,6 +7538,7 @@
       <c r="I223" t="n">
         <v>390.9915115700099</v>
       </c>
+      <c r="J223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -7387,6 +7570,7 @@
       <c r="I224" t="n">
         <v>378.064294086133</v>
       </c>
+      <c r="J224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -7418,6 +7602,7 @@
       <c r="I225" t="n">
         <v>378.064294086133</v>
       </c>
+      <c r="J225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -7449,6 +7634,7 @@
       <c r="I226" t="n">
         <v>383.7763030349461</v>
       </c>
+      <c r="J226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -7480,6 +7666,7 @@
       <c r="I227" t="n">
         <v>384.2070478388654</v>
       </c>
+      <c r="J227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -7511,6 +7698,7 @@
       <c r="I228" t="n">
         <v>377.0015368633445</v>
       </c>
+      <c r="J228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -7536,12 +7724,9 @@
       <c r="G229" t="n">
         <v>366</v>
       </c>
-      <c r="H229" t="n">
-        <v>537.8406409063098</v>
-      </c>
-      <c r="I229" t="n">
-        <v>1215.075038334197</v>
-      </c>
+      <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr"/>
+      <c r="J229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -7573,6 +7758,7 @@
       <c r="I230" t="n">
         <v>391.4732273066421</v>
       </c>
+      <c r="J230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -7604,6 +7790,7 @@
       <c r="I231" t="n">
         <v>401.6590360634859</v>
       </c>
+      <c r="J231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -7635,6 +7822,7 @@
       <c r="I232" t="n">
         <v>378.064294086133</v>
       </c>
+      <c r="J232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -7666,6 +7854,7 @@
       <c r="I233" t="n">
         <v>390.5097958333776</v>
       </c>
+      <c r="J233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -7697,6 +7886,7 @@
       <c r="I234" t="n">
         <v>377.7072913135326</v>
       </c>
+      <c r="J234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -7728,6 +7918,7 @@
       <c r="I235" t="n">
         <v>383.3455582310268</v>
       </c>
+      <c r="J235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -7759,6 +7950,7 @@
       <c r="I236" t="n">
         <v>383.7763030349461</v>
       </c>
+      <c r="J236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -7790,6 +7982,7 @@
       <c r="I237" t="n">
         <v>383.7763030349461</v>
       </c>
+      <c r="J237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -7821,6 +8014,7 @@
       <c r="I238" t="n">
         <v>377.3502885409321</v>
       </c>
+      <c r="J238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -7852,6 +8046,7 @@
       <c r="I239" t="n">
         <v>390.9915115700099</v>
       </c>
+      <c r="J239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -7883,6 +8078,7 @@
       <c r="I240" t="n">
         <v>402.3402720888473</v>
       </c>
+      <c r="J240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -7914,6 +8110,7 @@
       <c r="I241" t="n">
         <v>381.8569587182603</v>
       </c>
+      <c r="J241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -7945,6 +8142,7 @@
       <c r="I242" t="n">
         <v>390.9915115700099</v>
       </c>
+      <c r="J242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -7976,6 +8174,7 @@
       <c r="I243" t="n">
         <v>391.4732273066421</v>
       </c>
+      <c r="J243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -8007,6 +8206,7 @@
       <c r="I244" t="n">
         <v>383.7763030349461</v>
       </c>
+      <c r="J244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -8038,6 +8238,7 @@
       <c r="I245" t="n">
         <v>390.5097958333776</v>
       </c>
+      <c r="J245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -8069,6 +8270,7 @@
       <c r="I246" t="n">
         <v>380.8272745277539</v>
       </c>
+      <c r="J246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -8100,6 +8302,7 @@
       <c r="I247" t="n">
         <v>376.1480619672212</v>
       </c>
+      <c r="J247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -8131,6 +8334,7 @@
       <c r="I248" t="n">
         <v>377.7072913135326</v>
       </c>
+      <c r="J248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -8162,6 +8366,7 @@
       <c r="I249" t="n">
         <v>378.064294086133</v>
       </c>
+      <c r="J249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -8193,6 +8398,7 @@
       <c r="I250" t="n">
         <v>391.4732273066421</v>
       </c>
+      <c r="J250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -8224,6 +8430,7 @@
       <c r="I251" t="n">
         <v>384.2070478388654</v>
       </c>
+      <c r="J251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -8255,6 +8462,7 @@
       <c r="I252" t="n">
         <v>378.064294086133</v>
       </c>
+      <c r="J252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -8286,6 +8494,7 @@
       <c r="I253" t="n">
         <v>377.7072913135326</v>
       </c>
+      <c r="J253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -8317,6 +8526,7 @@
       <c r="I254" t="n">
         <v>377.7072913135326</v>
       </c>
+      <c r="J254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -8348,6 +8558,7 @@
       <c r="I255" t="n">
         <v>392.1217317084272</v>
       </c>
+      <c r="J255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -8379,6 +8590,7 @@
       <c r="I256" t="n">
         <v>400.9778000381246</v>
       </c>
+      <c r="J256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -8410,6 +8622,7 @@
       <c r="I257" t="n">
         <v>390.9915115700099</v>
       </c>
+      <c r="J257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -8441,6 +8654,7 @@
       <c r="I258" t="n">
         <v>384.2070478388654</v>
       </c>
+      <c r="J258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -8472,6 +8686,7 @@
       <c r="I259" t="n">
         <v>377.7072913135326</v>
       </c>
+      <c r="J259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -8503,6 +8718,7 @@
       <c r="I260" t="n">
         <v>377.7072913135326</v>
       </c>
+      <c r="J260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -8534,6 +8750,7 @@
       <c r="I261" t="n">
         <v>390.9915115700099</v>
       </c>
+      <c r="J261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -8565,6 +8782,7 @@
       <c r="I262" t="n">
         <v>380.8272745277539</v>
       </c>
+      <c r="J262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -8596,6 +8814,7 @@
       <c r="I263" t="n">
         <v>383.7763030349461</v>
       </c>
+      <c r="J263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -8627,6 +8846,7 @@
       <c r="I264" t="n">
         <v>427.1574300562969</v>
       </c>
+      <c r="J264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -8658,6 +8878,7 @@
       <c r="I265" t="n">
         <v>393.4842037591498</v>
       </c>
+      <c r="J265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -8689,6 +8910,7 @@
       <c r="I266" t="n">
         <v>384.6377926427848</v>
       </c>
+      <c r="J266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -8720,6 +8942,7 @@
       <c r="I267" t="n">
         <v>377.7072913135326</v>
       </c>
+      <c r="J267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -8751,6 +8974,7 @@
       <c r="I268" t="n">
         <v>388.5829328868485</v>
       </c>
+      <c r="J268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -8782,6 +9006,7 @@
       <c r="I269" t="n">
         <v>384.2070478388654</v>
       </c>
+      <c r="J269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -8813,6 +9038,7 @@
       <c r="I270" t="n">
         <v>377.3502885409321</v>
       </c>
+      <c r="J270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -8844,6 +9070,7 @@
       <c r="I271" t="n">
         <v>377.0567566800624</v>
       </c>
+      <c r="J271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -8875,6 +9102,7 @@
       <c r="I272" t="n">
         <v>393.4842037591498</v>
       </c>
+      <c r="J272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -8906,6 +9134,7 @@
       <c r="I273" t="n">
         <v>383.3455582310268</v>
       </c>
+      <c r="J273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -8937,6 +9166,7 @@
       <c r="I274" t="n">
         <v>390.9915115700099</v>
       </c>
+      <c r="J274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -8968,6 +9198,7 @@
       <c r="I275" t="n">
         <v>383.7763030349461</v>
       </c>
+      <c r="J275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -8999,6 +9230,7 @@
       <c r="I276" t="n">
         <v>390.5097958333776</v>
       </c>
+      <c r="J276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -9030,6 +9262,7 @@
       <c r="I277" t="n">
         <v>383.7763030349461</v>
       </c>
+      <c r="J277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -9061,6 +9294,7 @@
       <c r="I278" t="n">
         <v>377.3502885409321</v>
       </c>
+      <c r="J278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -9092,6 +9326,7 @@
       <c r="I279" t="n">
         <v>383.7763030349461</v>
       </c>
+      <c r="J279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -9123,6 +9358,7 @@
       <c r="I280" t="n">
         <v>384.6377926427848</v>
       </c>
+      <c r="J280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -9154,6 +9390,7 @@
       <c r="I281" t="n">
         <v>383.3455582310268</v>
       </c>
+      <c r="J281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -9185,6 +9422,7 @@
       <c r="I282" t="n">
         <v>377.3502885409321</v>
       </c>
+      <c r="J282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -9216,6 +9454,7 @@
       <c r="I283" t="n">
         <v>390.9915115700099</v>
       </c>
+      <c r="J283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -9247,6 +9486,7 @@
       <c r="I284" t="n">
         <v>390.5097958333776</v>
       </c>
+      <c r="J284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -9278,6 +9518,7 @@
       <c r="I285" t="n">
         <v>383.3455582310268</v>
       </c>
+      <c r="J285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -9309,6 +9550,7 @@
       <c r="I286" t="n">
         <v>376.1480619672212</v>
       </c>
+      <c r="J286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -9340,6 +9582,7 @@
       <c r="I287" t="n">
         <v>384.2070478388654</v>
       </c>
+      <c r="J287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -9371,6 +9614,7 @@
       <c r="I288" t="n">
         <v>383.3455582310268</v>
       </c>
+      <c r="J288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -9402,6 +9646,7 @@
       <c r="I289" t="n">
         <v>402.3402720888473</v>
       </c>
+      <c r="J289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -9433,6 +9678,7 @@
       <c r="I290" t="n">
         <v>383.7763030349461</v>
       </c>
+      <c r="J290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -9464,6 +9710,7 @@
       <c r="I291" t="n">
         <v>380.5633134943361</v>
       </c>
+      <c r="J291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -9495,6 +9742,7 @@
       <c r="I292" t="n">
         <v>401.6590360634859</v>
       </c>
+      <c r="J292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -9526,6 +9774,7 @@
       <c r="I293" t="n">
         <v>390.5097958333776</v>
       </c>
+      <c r="J293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -9557,6 +9806,7 @@
       <c r="I294" t="n">
         <v>377.3502885409321</v>
       </c>
+      <c r="J294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -9588,6 +9838,7 @@
       <c r="I295" t="n">
         <v>383.7763030349461</v>
       </c>
+      <c r="J295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -9619,6 +9870,7 @@
       <c r="I296" t="n">
         <v>376.5375025584389</v>
       </c>
+      <c r="J296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -9650,6 +9902,7 @@
       <c r="I297" t="n">
         <v>383.7763030349461</v>
       </c>
+      <c r="J297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -9681,6 +9934,7 @@
       <c r="I298" t="n">
         <v>391.4732273066421</v>
       </c>
+      <c r="J298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -9712,6 +9966,7 @@
       <c r="I299" t="n">
         <v>383.3455582310268</v>
       </c>
+      <c r="J299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -9743,6 +9998,7 @@
       <c r="I300" t="n">
         <v>391.4732273066421</v>
       </c>
+      <c r="J300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -9774,6 +10030,7 @@
       <c r="I301" t="n">
         <v>377.7072913135326</v>
       </c>
+      <c r="J301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -9805,6 +10062,7 @@
       <c r="I302" t="n">
         <v>384.6377926427848</v>
       </c>
+      <c r="J302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -9836,6 +10094,7 @@
       <c r="I303" t="n">
         <v>401.6590360634859</v>
       </c>
+      <c r="J303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -9867,6 +10126,7 @@
       <c r="I304" t="n">
         <v>377.7072913135326</v>
       </c>
+      <c r="J304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -9898,6 +10158,7 @@
       <c r="I305" t="n">
         <v>376.2778754976271</v>
       </c>
+      <c r="J305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -9929,6 +10190,7 @@
       <c r="I306" t="n">
         <v>390.9915115700099</v>
       </c>
+      <c r="J306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -9960,6 +10222,7 @@
       <c r="I307" t="n">
         <v>377.7072913135326</v>
       </c>
+      <c r="J307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -9991,6 +10254,7 @@
       <c r="I308" t="n">
         <v>376.0671194565065</v>
       </c>
+      <c r="J308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -10022,6 +10286,7 @@
       <c r="I309" t="n">
         <v>376.0671194565065</v>
       </c>
+      <c r="J309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -10053,6 +10318,7 @@
       <c r="I310" t="n">
         <v>383.3455582310268</v>
       </c>
+      <c r="J310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -10084,6 +10350,7 @@
       <c r="I311" t="n">
         <v>377.7072913135326</v>
       </c>
+      <c r="J311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -10115,6 +10382,7 @@
       <c r="I312" t="n">
         <v>377.0015368633445</v>
       </c>
+      <c r="J312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -10146,6 +10414,7 @@
       <c r="I313" t="n">
         <v>377.0015368633445</v>
       </c>
+      <c r="J313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -10177,6 +10446,7 @@
       <c r="I314" t="n">
         <v>376.0671194565065</v>
       </c>
+      <c r="J314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -10208,6 +10478,7 @@
       <c r="I315" t="n">
         <v>376.2778754976271</v>
       </c>
+      <c r="J315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -10239,6 +10510,7 @@
       <c r="I316" t="n">
         <v>383.7763030349461</v>
       </c>
+      <c r="J316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -10270,6 +10542,7 @@
       <c r="I317" t="n">
         <v>390.9915115700099</v>
       </c>
+      <c r="J317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -10301,6 +10574,7 @@
       <c r="I318" t="n">
         <v>376.1480619672212</v>
       </c>
+      <c r="J318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -10332,6 +10606,7 @@
       <c r="I319" t="n">
         <v>383.7763030349461</v>
       </c>
+      <c r="J319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -10363,6 +10638,7 @@
       <c r="I320" t="n">
         <v>390.9915115700099</v>
       </c>
+      <c r="J320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -10394,6 +10670,7 @@
       <c r="I321" t="n">
         <v>377.7072913135326</v>
       </c>
+      <c r="J321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -10425,6 +10702,7 @@
       <c r="I322" t="n">
         <v>390.9915115700099</v>
       </c>
+      <c r="J322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -10456,6 +10734,7 @@
       <c r="I323" t="n">
         <v>400.2965640127633</v>
       </c>
+      <c r="J323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -10487,6 +10766,7 @@
       <c r="I324" t="n">
         <v>390.5097958333776</v>
       </c>
+      <c r="J324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -10518,6 +10798,7 @@
       <c r="I325" t="n">
         <v>382.9148134271074</v>
       </c>
+      <c r="J325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -10549,6 +10830,7 @@
       <c r="I326" t="n">
         <v>382.9148134271074</v>
       </c>
+      <c r="J326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -10580,6 +10862,7 @@
       <c r="I327" t="n">
         <v>401.6590360634859</v>
       </c>
+      <c r="J327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -10611,6 +10894,7 @@
       <c r="I328" t="n">
         <v>384.2070478388654</v>
       </c>
+      <c r="J328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -10642,6 +10926,7 @@
       <c r="I329" t="n">
         <v>384.2070478388654</v>
       </c>
+      <c r="J329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -10673,6 +10958,7 @@
       <c r="I330" t="n">
         <v>384.2070478388654</v>
       </c>
+      <c r="J330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -10704,6 +10990,7 @@
       <c r="I331" t="n">
         <v>390.5097958333776</v>
       </c>
+      <c r="J331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -10735,6 +11022,7 @@
       <c r="I332" t="n">
         <v>384.2070478388654</v>
       </c>
+      <c r="J332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -10766,6 +11054,7 @@
       <c r="I333" t="n">
         <v>401.6590360634859</v>
       </c>
+      <c r="J333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -10797,6 +11086,7 @@
       <c r="I334" t="n">
         <v>390.9915115700099</v>
       </c>
+      <c r="J334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -10828,6 +11118,7 @@
       <c r="I335" t="n">
         <v>386.7915166623815</v>
       </c>
+      <c r="J335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -10859,6 +11150,7 @@
       <c r="I336" t="n">
         <v>378.7782996313338</v>
       </c>
+      <c r="J336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -10890,6 +11182,7 @@
       <c r="I337" t="n">
         <v>379.1353024039344</v>
       </c>
+      <c r="J337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -10921,6 +11214,7 @@
       <c r="I338" t="n">
         <v>384.6377926427848</v>
       </c>
+      <c r="J338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -10952,6 +11246,7 @@
       <c r="I339" t="n">
         <v>377.7072913135326</v>
       </c>
+      <c r="J339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -10983,6 +11278,7 @@
       <c r="I340" t="n">
         <v>392.8029677337885</v>
       </c>
+      <c r="J340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -11014,6 +11310,7 @@
       <c r="I341" t="n">
         <v>392.1217317084272</v>
       </c>
+      <c r="J341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -11045,6 +11342,7 @@
       <c r="I342" t="n">
         <v>376.0671194565065</v>
       </c>
+      <c r="J342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -11076,6 +11374,7 @@
       <c r="I343" t="n">
         <v>385.0685374467042</v>
       </c>
+      <c r="J343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -11107,6 +11406,7 @@
       <c r="I344" t="n">
         <v>392.1217317084272</v>
       </c>
+      <c r="J344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -11138,6 +11438,7 @@
       <c r="I345" t="n">
         <v>377.7072913135326</v>
       </c>
+      <c r="J345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -11167,8 +11468,9 @@
         <v>382.6170320199877</v>
       </c>
       <c r="I346" t="n">
-        <v>382.4840686231881</v>
-      </c>
+        <v>382.484068623188</v>
+      </c>
+      <c r="J346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -11200,6 +11502,7 @@
       <c r="I347" t="n">
         <v>385.0685374467042</v>
       </c>
+      <c r="J347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -11231,6 +11534,7 @@
       <c r="I348" t="n">
         <v>382.484068623188</v>
       </c>
+      <c r="J348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -11262,6 +11566,7 @@
       <c r="I349" t="n">
         <v>390.9915115700099</v>
       </c>
+      <c r="J349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -11293,6 +11598,7 @@
       <c r="I350" t="n">
         <v>386.3607718584621</v>
       </c>
+      <c r="J350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -11324,6 +11630,7 @@
       <c r="I351" t="n">
         <v>391.4732273066421</v>
       </c>
+      <c r="J351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -11355,6 +11662,7 @@
       <c r="I352" t="n">
         <v>375.9959153668595</v>
       </c>
+      <c r="J352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -11386,6 +11694,7 @@
       <c r="I353" t="n">
         <v>385.1134385388678</v>
       </c>
+      <c r="J353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -11417,6 +11726,7 @@
       <c r="I354" t="n">
         <v>378.064294086133</v>
       </c>
+      <c r="J354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -11448,6 +11758,7 @@
       <c r="I355" t="n">
         <v>384.6377926427848</v>
       </c>
+      <c r="J355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -11479,6 +11790,7 @@
       <c r="I356" t="n">
         <v>377.7072913135326</v>
       </c>
+      <c r="J356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -11510,6 +11822,7 @@
       <c r="I357" t="n">
         <v>391.4732273066421</v>
       </c>
+      <c r="J357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -11541,6 +11854,7 @@
       <c r="I358" t="n">
         <v>378.064294086133</v>
       </c>
+      <c r="J358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -11572,6 +11886,7 @@
       <c r="I359" t="n">
         <v>377.7072913135326</v>
       </c>
+      <c r="J359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -11603,6 +11918,7 @@
       <c r="I360" t="n">
         <v>384.6377926427848</v>
       </c>
+      <c r="J360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -11634,6 +11950,7 @@
       <c r="I361" t="n">
         <v>391.4732273066421</v>
       </c>
+      <c r="J361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -11665,6 +11982,7 @@
       <c r="I362" t="n">
         <v>385.0685374467042</v>
       </c>
+      <c r="J362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -11696,6 +12014,7 @@
       <c r="I363" t="n">
         <v>379.1353024039344</v>
       </c>
+      <c r="J363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -11727,6 +12046,7 @@
       <c r="I364" t="n">
         <v>378.4212968587335</v>
       </c>
+      <c r="J364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -11758,6 +12078,7 @@
       <c r="I365" t="n">
         <v>391.4732273066421</v>
       </c>
+      <c r="J365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -11789,6 +12110,7 @@
       <c r="I366" t="n">
         <v>378.064294086133</v>
       </c>
+      <c r="J366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -11820,6 +12142,7 @@
       <c r="I367" t="n">
         <v>385.0685374467042</v>
       </c>
+      <c r="J367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -11851,6 +12174,7 @@
       <c r="I368" t="n">
         <v>376.1480619672212</v>
       </c>
+      <c r="J368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -11882,6 +12206,7 @@
       <c r="I369" t="n">
         <v>390.9915115700099</v>
       </c>
+      <c r="J369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -11913,6 +12238,7 @@
       <c r="I370" t="n">
         <v>376.0540775245338</v>
       </c>
+      <c r="J370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -11944,6 +12270,7 @@
       <c r="I371" t="n">
         <v>384.2070478388654</v>
       </c>
+      <c r="J371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -11975,6 +12302,7 @@
       <c r="I372" t="n">
         <v>402.3402720888473</v>
       </c>
+      <c r="J372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -12006,6 +12334,7 @@
       <c r="I373" t="n">
         <v>384.2070478388654</v>
       </c>
+      <c r="J373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -12037,6 +12366,7 @@
       <c r="I374" t="n">
         <v>384.2070478388654</v>
       </c>
+      <c r="J374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -12068,6 +12398,7 @@
       <c r="I375" t="n">
         <v>381.277319039537</v>
       </c>
+      <c r="J375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -12099,6 +12430,7 @@
       <c r="I376" t="n">
         <v>393.0334756174935</v>
       </c>
+      <c r="J376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -12130,6 +12462,7 @@
       <c r="I377" t="n">
         <v>391.4732273066421</v>
       </c>
+      <c r="J377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -12161,6 +12494,7 @@
       <c r="I378" t="n">
         <v>428.0858811575557</v>
       </c>
+      <c r="J378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -12192,6 +12526,7 @@
       <c r="I379" t="n">
         <v>391.4732273066421</v>
       </c>
+      <c r="J379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -12223,6 +12558,7 @@
       <c r="I380" t="n">
         <v>392.1720956060504</v>
       </c>
+      <c r="J380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -12248,12 +12584,9 @@
       <c r="G381" t="n">
         <v>391</v>
       </c>
-      <c r="H381" t="n">
-        <v>286.0807053975354</v>
-      </c>
-      <c r="I381" t="n">
-        <v>755.6533924255357</v>
-      </c>
+      <c r="H381" t="inlineStr"/>
+      <c r="I381" t="inlineStr"/>
+      <c r="J381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -12285,6 +12618,7 @@
       <c r="I382" t="n">
         <v>384.2070478388654</v>
       </c>
+      <c r="J382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -12316,6 +12650,7 @@
       <c r="I383" t="n">
         <v>390.9915115700099</v>
       </c>
+      <c r="J383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -12347,6 +12682,7 @@
       <c r="I384" t="n">
         <v>376.1480619672212</v>
       </c>
+      <c r="J384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -12378,6 +12714,7 @@
       <c r="I385" t="n">
         <v>384.2070478388654</v>
       </c>
+      <c r="J385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -12409,6 +12746,7 @@
       <c r="I386" t="n">
         <v>385.0685374467042</v>
       </c>
+      <c r="J386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -12440,6 +12778,7 @@
       <c r="I387" t="n">
         <v>377.7072913135326</v>
       </c>
+      <c r="J387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -12471,6 +12810,7 @@
       <c r="I388" t="n">
         <v>384.2070478388654</v>
       </c>
+      <c r="J388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -12502,6 +12842,7 @@
       <c r="I389" t="n">
         <v>383.7763030349461</v>
       </c>
+      <c r="J389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -12533,6 +12874,7 @@
       <c r="I390" t="n">
         <v>378.064294086133</v>
       </c>
+      <c r="J390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -12564,6 +12906,7 @@
       <c r="I391" t="n">
         <v>376.407689028033</v>
       </c>
+      <c r="J391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -12595,6 +12938,7 @@
       <c r="I392" t="n">
         <v>377.7072913135326</v>
       </c>
+      <c r="J392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -12626,6 +12970,7 @@
       <c r="I393" t="n">
         <v>378.064294086133</v>
       </c>
+      <c r="J393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -12657,6 +13002,7 @@
       <c r="I394" t="n">
         <v>383.7763030349461</v>
       </c>
+      <c r="J394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -12688,6 +13034,7 @@
       <c r="I395" t="n">
         <v>381.8569587182603</v>
       </c>
+      <c r="J395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -12719,6 +13066,7 @@
       <c r="I396" t="n">
         <v>378.064294086133</v>
       </c>
+      <c r="J396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -12750,6 +13098,7 @@
       <c r="I397" t="n">
         <v>383.7763030349461</v>
       </c>
+      <c r="J397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -12781,6 +13130,7 @@
       <c r="I398" t="n">
         <v>377.7072913135326</v>
       </c>
+      <c r="J398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -12812,6 +13162,7 @@
       <c r="I399" t="n">
         <v>391.4732273066421</v>
       </c>
+      <c r="J399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -12843,6 +13194,7 @@
       <c r="I400" t="n">
         <v>383.3455582310268</v>
       </c>
+      <c r="J400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -12874,6 +13226,7 @@
       <c r="I401" t="n">
         <v>383.7763030349461</v>
       </c>
+      <c r="J401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -12905,6 +13258,7 @@
       <c r="I402" t="n">
         <v>403.0215081142086</v>
       </c>
+      <c r="J402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -12936,6 +13290,7 @@
       <c r="I403" t="n">
         <v>379.1353024039344</v>
       </c>
+      <c r="J403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -12967,6 +13322,7 @@
       <c r="I404" t="n">
         <v>385.4992822506235</v>
       </c>
+      <c r="J404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -12998,6 +13354,7 @@
       <c r="I405" t="n">
         <v>394.1654397845111</v>
       </c>
+      <c r="J405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -13029,6 +13386,7 @@
       <c r="I406" t="n">
         <v>394.8466758098725</v>
       </c>
+      <c r="J406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -13060,6 +13418,7 @@
       <c r="I407" t="n">
         <v>378.4212968587335</v>
       </c>
+      <c r="J407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -13091,6 +13450,7 @@
       <c r="I408" t="n">
         <v>377.7072913135326</v>
       </c>
+      <c r="J408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -13122,6 +13482,7 @@
       <c r="I409" t="n">
         <v>375.9959153668595</v>
       </c>
+      <c r="J409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -13153,6 +13514,7 @@
       <c r="I410" t="n">
         <v>384.2070478388654</v>
       </c>
+      <c r="J410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -13184,6 +13546,7 @@
       <c r="I411" t="n">
         <v>392.8029677337885</v>
       </c>
+      <c r="J411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -13215,6 +13578,7 @@
       <c r="I412" t="n">
         <v>416.5175121106006</v>
       </c>
+      <c r="J412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -13246,6 +13610,7 @@
       <c r="I413" t="n">
         <v>380.8272745277539</v>
       </c>
+      <c r="J413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -13277,6 +13642,7 @@
       <c r="I414" t="n">
         <v>392.8029677337885</v>
       </c>
+      <c r="J414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -13308,6 +13674,7 @@
       <c r="I415" t="n">
         <v>384.6377926427848</v>
       </c>
+      <c r="J415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -13339,6 +13706,7 @@
       <c r="I416" t="n">
         <v>392.1217317084272</v>
       </c>
+      <c r="J416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -13370,6 +13738,7 @@
       <c r="I417" t="n">
         <v>378.4212968587335</v>
       </c>
+      <c r="J417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -13395,11 +13764,12 @@
       <c r="G418" t="n">
         <v>377</v>
       </c>
-      <c r="H418" t="n">
-        <v>250.3580118456147</v>
-      </c>
-      <c r="I418" t="n">
-        <v>950.3343520876629</v>
+      <c r="H418" t="inlineStr"/>
+      <c r="I418" t="inlineStr"/>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>Invalid</t>
+        </is>
       </c>
     </row>
     <row r="419">
@@ -13432,6 +13802,7 @@
       <c r="I419" t="n">
         <v>403.0215081142086</v>
       </c>
+      <c r="J419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -13463,6 +13834,7 @@
       <c r="I420" t="n">
         <v>389.0646486234808</v>
       </c>
+      <c r="J420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -13494,6 +13866,7 @@
       <c r="I421" t="n">
         <v>384.6377926427848</v>
       </c>
+      <c r="J421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -13525,6 +13898,7 @@
       <c r="I422" t="n">
         <v>384.6377926427848</v>
       </c>
+      <c r="J422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -13556,6 +13930,7 @@
       <c r="I423" t="n">
         <v>390.9915115700099</v>
       </c>
+      <c r="J423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -13587,6 +13962,7 @@
       <c r="I424" t="n">
         <v>385.0685374467042</v>
       </c>
+      <c r="J424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -13618,6 +13994,7 @@
       <c r="I425" t="n">
         <v>403.70274413957</v>
       </c>
+      <c r="J425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -13649,6 +14026,7 @@
       <c r="I426" t="n">
         <v>378.064294086133</v>
       </c>
+      <c r="J426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -13680,6 +14058,7 @@
       <c r="I427" t="n">
         <v>377.7072913135326</v>
       </c>
+      <c r="J427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -13711,6 +14090,7 @@
       <c r="I428" t="n">
         <v>378.4212968587335</v>
       </c>
+      <c r="J428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -13742,6 +14122,7 @@
       <c r="I429" t="n">
         <v>392.8029677337885</v>
       </c>
+      <c r="J429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -13773,6 +14154,7 @@
       <c r="I430" t="n">
         <v>390.9915115700099</v>
       </c>
+      <c r="J430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -13804,6 +14186,7 @@
       <c r="I431" t="n">
         <v>383.7763030349461</v>
       </c>
+      <c r="J431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -13835,6 +14218,7 @@
       <c r="I432" t="n">
         <v>385.0685374467042</v>
       </c>
+      <c r="J432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -13866,6 +14250,7 @@
       <c r="I433" t="n">
         <v>392.1217317084272</v>
       </c>
+      <c r="J433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -13897,6 +14282,7 @@
       <c r="I434" t="n">
         <v>377.7072913135326</v>
       </c>
+      <c r="J434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -13928,6 +14314,7 @@
       <c r="I435" t="n">
         <v>384.6377926427848</v>
       </c>
+      <c r="J435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -13959,6 +14346,7 @@
       <c r="I436" t="n">
         <v>376.7971296192507</v>
       </c>
+      <c r="J436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -13990,6 +14378,7 @@
       <c r="I437" t="n">
         <v>384.2070478388654</v>
       </c>
+      <c r="J437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -14021,6 +14410,7 @@
       <c r="I438" t="n">
         <v>384.2070478388654</v>
       </c>
+      <c r="J438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -14052,6 +14442,7 @@
       <c r="I439" t="n">
         <v>378.064294086133</v>
       </c>
+      <c r="J439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -14083,6 +14474,7 @@
       <c r="I440" t="n">
         <v>383.3455582310268</v>
       </c>
+      <c r="J440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -14114,6 +14506,7 @@
       <c r="I441" t="n">
         <v>391.4732273066421</v>
       </c>
+      <c r="J441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -14145,6 +14538,7 @@
       <c r="I442" t="n">
         <v>384.2070478388654</v>
       </c>
+      <c r="J442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -14176,6 +14570,7 @@
       <c r="I443" t="n">
         <v>376.1480619672212</v>
       </c>
+      <c r="J443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -14207,6 +14602,7 @@
       <c r="I444" t="n">
         <v>392.1217317084272</v>
       </c>
+      <c r="J444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -14238,6 +14634,7 @@
       <c r="I445" t="n">
         <v>376.0671194565065</v>
       </c>
+      <c r="J445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -14269,6 +14666,7 @@
       <c r="I446" t="n">
         <v>384.2070478388654</v>
       </c>
+      <c r="J446" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -14300,6 +14698,7 @@
       <c r="I447" t="n">
         <v>403.0215081142086</v>
       </c>
+      <c r="J447" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -14331,6 +14730,7 @@
       <c r="I448" t="n">
         <v>375.9603133220361</v>
       </c>
+      <c r="J448" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -14362,6 +14762,7 @@
       <c r="I449" t="n">
         <v>390.9915115700099</v>
       </c>
+      <c r="J449" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -14393,6 +14794,7 @@
       <c r="I450" t="n">
         <v>383.0122541276269</v>
       </c>
+      <c r="J450" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -14424,6 +14826,7 @@
       <c r="I451" t="n">
         <v>377.7072913135326</v>
       </c>
+      <c r="J451" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" t="n">
@@ -14455,6 +14858,7 @@
       <c r="I452" t="n">
         <v>377.7072913135326</v>
       </c>
+      <c r="J452" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" t="n">
@@ -14486,6 +14890,7 @@
       <c r="I453" t="n">
         <v>382.9148134271074</v>
       </c>
+      <c r="J453" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -14517,6 +14922,7 @@
       <c r="I454" t="n">
         <v>376.1480619672212</v>
       </c>
+      <c r="J454" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -14548,6 +14954,7 @@
       <c r="I455" t="n">
         <v>377.7072913135326</v>
       </c>
+      <c r="J455" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -14579,6 +14986,7 @@
       <c r="I456" t="n">
         <v>391.4732273066421</v>
       </c>
+      <c r="J456" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -14610,6 +15018,7 @@
       <c r="I457" t="n">
         <v>378.064294086133</v>
       </c>
+      <c r="J457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" t="n">
@@ -14641,6 +15050,7 @@
       <c r="I458" t="n">
         <v>378.064294086133</v>
       </c>
+      <c r="J458" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" t="n">
@@ -14672,6 +15082,7 @@
       <c r="I459" t="n">
         <v>403.0215081142086</v>
       </c>
+      <c r="J459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" t="n">
@@ -14703,6 +15114,7 @@
       <c r="I460" t="n">
         <v>380.5633134943361</v>
       </c>
+      <c r="J460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" t="n">
@@ -14734,6 +15146,7 @@
       <c r="I461" t="n">
         <v>379.8493079491352</v>
       </c>
+      <c r="J461" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -14759,12 +15172,9 @@
       <c r="G462" t="n">
         <v>340</v>
       </c>
-      <c r="H462" t="n">
-        <v>264.817197330916</v>
-      </c>
-      <c r="I462" t="n">
-        <v>871.5349160339448</v>
-      </c>
+      <c r="H462" t="inlineStr"/>
+      <c r="I462" t="inlineStr"/>
+      <c r="J462" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" t="n">
@@ -14796,6 +15206,7 @@
       <c r="I463" t="n">
         <v>392.1217317084272</v>
       </c>
+      <c r="J463" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" t="n">
@@ -14821,12 +15232,9 @@
       <c r="G464" t="n">
         <v>382</v>
       </c>
-      <c r="H464" t="n">
-        <v>524.6572659050057</v>
-      </c>
-      <c r="I464" t="n">
-        <v>1128.556212831731</v>
-      </c>
+      <c r="H464" t="inlineStr"/>
+      <c r="I464" t="inlineStr"/>
+      <c r="J464" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" t="n">
@@ -14858,6 +15266,7 @@
       <c r="I465" t="n">
         <v>404.3839801649313</v>
       </c>
+      <c r="J465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" t="n">
@@ -14889,6 +15298,7 @@
       <c r="I466" t="n">
         <v>383.3455582310268</v>
       </c>
+      <c r="J466" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" t="n">
@@ -14920,6 +15330,7 @@
       <c r="I467" t="n">
         <v>377.3502885409321</v>
       </c>
+      <c r="J467" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" t="n">
@@ -14951,6 +15362,7 @@
       <c r="I468" t="n">
         <v>401.6590360634859</v>
       </c>
+      <c r="J468" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" t="n">
@@ -14982,6 +15394,7 @@
       <c r="I469" t="n">
         <v>375.959536901601</v>
       </c>
+      <c r="J469" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" t="n">
@@ -15013,6 +15426,7 @@
       <c r="I470" t="n">
         <v>376.0671194565065</v>
       </c>
+      <c r="J470" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" t="n">
@@ -15044,6 +15458,7 @@
       <c r="I471" t="n">
         <v>384.2070478388654</v>
       </c>
+      <c r="J471" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" t="n">
@@ -15069,12 +15484,9 @@
       <c r="G472" t="n">
         <v>420</v>
       </c>
-      <c r="H472" t="n">
-        <v>292.8850279788536</v>
-      </c>
-      <c r="I472" t="n">
-        <v>718.5713048708448</v>
-      </c>
+      <c r="H472" t="inlineStr"/>
+      <c r="I472" t="inlineStr"/>
+      <c r="J472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" t="n">
@@ -15106,6 +15518,7 @@
       <c r="I473" t="n">
         <v>376.2778754976271</v>
       </c>
+      <c r="J473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" t="n">
@@ -15137,6 +15550,7 @@
       <c r="I474" t="n">
         <v>383.3455582310268</v>
       </c>
+      <c r="J474" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" t="n">
@@ -15168,6 +15582,7 @@
       <c r="I475" t="n">
         <v>392.1217317084272</v>
       </c>
+      <c r="J475" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" t="n">
@@ -15199,6 +15614,7 @@
       <c r="I476" t="n">
         <v>375.9959153668595</v>
       </c>
+      <c r="J476" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" t="n">
@@ -15230,6 +15646,7 @@
       <c r="I477" t="n">
         <v>385.0685374467042</v>
       </c>
+      <c r="J477" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" t="n">
@@ -15261,6 +15678,7 @@
       <c r="I478" t="n">
         <v>394.1654397845111</v>
       </c>
+      <c r="J478" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" t="n">
@@ -15292,6 +15710,7 @@
       <c r="I479" t="n">
         <v>378.064294086133</v>
       </c>
+      <c r="J479" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" t="n">
@@ -15323,6 +15742,7 @@
       <c r="I480" t="n">
         <v>390.9915115700099</v>
       </c>
+      <c r="J480" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" t="n">
@@ -15348,12 +15768,9 @@
       <c r="G481" t="n">
         <v>393</v>
       </c>
-      <c r="H481" t="n">
-        <v>545.4955038102927</v>
-      </c>
-      <c r="I481" t="n">
-        <v>1265.311775722726</v>
-      </c>
+      <c r="H481" t="inlineStr"/>
+      <c r="I481" t="inlineStr"/>
+      <c r="J481" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" t="n">
@@ -15385,6 +15802,7 @@
       <c r="I482" t="n">
         <v>376.9269431496566</v>
       </c>
+      <c r="J482" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" t="n">
@@ -15416,6 +15834,7 @@
       <c r="I483" t="n">
         <v>376.0671194565065</v>
       </c>
+      <c r="J483" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" t="n">
@@ -15445,8 +15864,9 @@
         <v>384.7433828266497</v>
       </c>
       <c r="I484" t="n">
-        <v>384.6377926427848</v>
-      </c>
+        <v>384.6377926427847</v>
+      </c>
+      <c r="J484" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" t="n">
@@ -15478,6 +15898,7 @@
       <c r="I485" t="n">
         <v>383.7763030349461</v>
       </c>
+      <c r="J485" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" t="n">
@@ -15509,6 +15930,7 @@
       <c r="I486" t="n">
         <v>381.8569587182603</v>
       </c>
+      <c r="J486" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" t="n">
@@ -15540,6 +15962,7 @@
       <c r="I487" t="n">
         <v>377.7072913135326</v>
       </c>
+      <c r="J487" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" t="n">
@@ -15571,6 +15994,7 @@
       <c r="I488" t="n">
         <v>377.7072913135326</v>
       </c>
+      <c r="J488" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" t="n">
@@ -15602,6 +16026,7 @@
       <c r="I489" t="n">
         <v>388.1012171502162</v>
       </c>
+      <c r="J489" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" t="n">
@@ -15627,11 +16052,12 @@
       <c r="G490" t="n">
         <v>383</v>
       </c>
-      <c r="H490" t="n">
-        <v>731.7638344738791</v>
-      </c>
-      <c r="I490" t="n">
-        <v>2492.711817982796</v>
+      <c r="H490" t="inlineStr"/>
+      <c r="I490" t="inlineStr"/>
+      <c r="J490" t="inlineStr">
+        <is>
+          <t>Invalid</t>
+        </is>
       </c>
     </row>
     <row r="491">
@@ -15664,6 +16090,7 @@
       <c r="I491" t="n">
         <v>377.0015368633445</v>
       </c>
+      <c r="J491" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" t="n">
@@ -15695,6 +16122,7 @@
       <c r="I492" t="n">
         <v>391.4732273066421</v>
       </c>
+      <c r="J492" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" t="n">
@@ -15726,6 +16154,7 @@
       <c r="I493" t="n">
         <v>390.5097958333776</v>
       </c>
+      <c r="J493" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" t="n">
@@ -15757,6 +16186,7 @@
       <c r="I494" t="n">
         <v>390.9915115700099</v>
       </c>
+      <c r="J494" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" t="n">
@@ -15788,6 +16218,7 @@
       <c r="I495" t="n">
         <v>377.3502885409321</v>
       </c>
+      <c r="J495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" t="n">
@@ -15819,6 +16250,7 @@
       <c r="I496" t="n">
         <v>378.064294086133</v>
       </c>
+      <c r="J496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" t="n">
@@ -15850,6 +16282,7 @@
       <c r="I497" t="n">
         <v>384.2070478388654</v>
       </c>
+      <c r="J497" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" t="n">
@@ -15875,11 +16308,12 @@
       <c r="G498" t="n">
         <v>410</v>
       </c>
-      <c r="H498" t="n">
-        <v>278.4258424935524</v>
-      </c>
-      <c r="I498" t="n">
-        <v>797.3707409245629</v>
+      <c r="H498" t="inlineStr"/>
+      <c r="I498" t="inlineStr"/>
+      <c r="J498" t="inlineStr">
+        <is>
+          <t>Invalid</t>
+        </is>
       </c>
     </row>
     <row r="499">
@@ -15912,6 +16346,7 @@
       <c r="I499" t="n">
         <v>383.7763030349461</v>
       </c>
+      <c r="J499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" t="n">
@@ -15943,6 +16378,7 @@
       <c r="I500" t="n">
         <v>382.9148134271074</v>
       </c>
+      <c r="J500" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" t="n">
@@ -15974,6 +16410,7 @@
       <c r="I501" t="n">
         <v>390.9915115700099</v>
       </c>
+      <c r="J501" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" t="n">
@@ -16005,6 +16442,7 @@
       <c r="I502" t="n">
         <v>383.7763030349461</v>
       </c>
+      <c r="J502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" t="n">
@@ -16036,6 +16474,7 @@
       <c r="I503" t="n">
         <v>390.9915115700099</v>
       </c>
+      <c r="J503" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" t="n">
@@ -16067,6 +16506,7 @@
       <c r="I504" t="n">
         <v>390.9915115700099</v>
       </c>
+      <c r="J504" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" t="n">
@@ -16098,6 +16538,7 @@
       <c r="I505" t="n">
         <v>377.3502885409321</v>
       </c>
+      <c r="J505" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" t="n">
@@ -16129,6 +16570,7 @@
       <c r="I506" t="n">
         <v>377.7072913135326</v>
       </c>
+      <c r="J506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" t="n">
@@ -16160,6 +16602,7 @@
       <c r="I507" t="n">
         <v>377.7072913135326</v>
       </c>
+      <c r="J507" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" t="n">
@@ -16191,6 +16634,7 @@
       <c r="I508" t="n">
         <v>393.0334756174935</v>
       </c>
+      <c r="J508" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" t="n">
@@ -16222,6 +16666,7 @@
       <c r="I509" t="n">
         <v>376.407689028033</v>
       </c>
+      <c r="J509" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" t="n">
@@ -16253,6 +16698,7 @@
       <c r="I510" t="n">
         <v>377.3502885409321</v>
       </c>
+      <c r="J510" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" t="n">
@@ -16284,6 +16730,7 @@
       <c r="I511" t="n">
         <v>380.8272745277539</v>
       </c>
+      <c r="J511" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" t="n">
@@ -16315,6 +16762,7 @@
       <c r="I512" t="n">
         <v>390.9915115700099</v>
       </c>
+      <c r="J512" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" t="n">
@@ -16346,6 +16794,7 @@
       <c r="I513" t="n">
         <v>484.8800469241788</v>
       </c>
+      <c r="J513" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" t="n">
@@ -16377,6 +16826,7 @@
       <c r="I514" t="n">
         <v>382.9148134271074</v>
       </c>
+      <c r="J514" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" t="n">
@@ -16408,6 +16858,7 @@
       <c r="I515" t="n">
         <v>390.5097958333776</v>
       </c>
+      <c r="J515" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" t="n">
@@ -16439,6 +16890,7 @@
       <c r="I516" t="n">
         <v>377.7072913135326</v>
       </c>
+      <c r="J516" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" t="n">
@@ -16470,6 +16922,7 @@
       <c r="I517" t="n">
         <v>402.3402720888473</v>
       </c>
+      <c r="J517" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" t="n">
@@ -16501,6 +16954,7 @@
       <c r="I518" t="n">
         <v>384.2070478388654</v>
       </c>
+      <c r="J518" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" t="n">
@@ -16532,6 +16986,7 @@
       <c r="I519" t="n">
         <v>376.7667168065594</v>
       </c>
+      <c r="J519" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" t="n">
@@ -16563,6 +17018,7 @@
       <c r="I520" t="n">
         <v>384.2070478388654</v>
       </c>
+      <c r="J520" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" t="n">
@@ -16594,6 +17050,7 @@
       <c r="I521" t="n">
         <v>376.2778754976271</v>
       </c>
+      <c r="J521" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" t="n">
@@ -16625,6 +17082,7 @@
       <c r="I522" t="n">
         <v>376.1480619672212</v>
       </c>
+      <c r="J522" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" t="n">
@@ -16656,6 +17114,7 @@
       <c r="I523" t="n">
         <v>376.6673160888447</v>
       </c>
+      <c r="J523" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" t="n">
@@ -16681,12 +17140,9 @@
       <c r="G524" t="n">
         <v>359</v>
       </c>
-      <c r="H524" t="n">
-        <v>260.1392255562597</v>
-      </c>
-      <c r="I524" t="n">
-        <v>897.0288512277947</v>
-      </c>
+      <c r="H524" t="inlineStr"/>
+      <c r="I524" t="inlineStr"/>
+      <c r="J524" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" t="n">
@@ -16718,6 +17174,7 @@
       <c r="I525" t="n">
         <v>391.4732273066421</v>
       </c>
+      <c r="J525" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" t="n">
@@ -16749,6 +17206,7 @@
       <c r="I526" t="n">
         <v>377.3502885409321</v>
       </c>
+      <c r="J526" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" t="n">
@@ -16780,6 +17238,7 @@
       <c r="I527" t="n">
         <v>401.6590360634859</v>
       </c>
+      <c r="J527" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" t="n">
@@ -16811,6 +17270,7 @@
       <c r="I528" t="n">
         <v>377.3502885409321</v>
       </c>
+      <c r="J528" t="inlineStr"/>
     </row>
     <row r="529">
       <c r="A529" t="n">
@@ -16842,6 +17302,7 @@
       <c r="I529" t="n">
         <v>377.7072913135326</v>
       </c>
+      <c r="J529" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" t="n">
@@ -16873,6 +17334,7 @@
       <c r="I530" t="n">
         <v>381.3421166230071</v>
       </c>
+      <c r="J530" t="inlineStr"/>
     </row>
     <row r="531">
       <c r="A531" t="n">
@@ -16904,6 +17366,7 @@
       <c r="I531" t="n">
         <v>377.7072913135326</v>
       </c>
+      <c r="J531" t="inlineStr"/>
     </row>
     <row r="532">
       <c r="A532" t="n">
@@ -16935,6 +17398,7 @@
       <c r="I532" t="n">
         <v>377.3502885409321</v>
       </c>
+      <c r="J532" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" t="n">
@@ -16966,6 +17430,7 @@
       <c r="I533" t="n">
         <v>377.3502885409321</v>
       </c>
+      <c r="J533" t="inlineStr"/>
     </row>
     <row r="534">
       <c r="A534" t="n">
@@ -16997,6 +17462,7 @@
       <c r="I534" t="n">
         <v>377.3502885409321</v>
       </c>
+      <c r="J534" t="inlineStr"/>
     </row>
     <row r="535">
       <c r="A535" t="n">
@@ -17028,6 +17494,7 @@
       <c r="I535" t="n">
         <v>382.3718008135135</v>
       </c>
+      <c r="J535" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" t="n">
@@ -17059,6 +17526,7 @@
       <c r="I536" t="n">
         <v>378.064294086133</v>
       </c>
+      <c r="J536" t="inlineStr"/>
     </row>
     <row r="537">
       <c r="A537" t="n">
@@ -17090,6 +17558,7 @@
       <c r="I537" t="n">
         <v>382.3718008135135</v>
       </c>
+      <c r="J537" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" t="n">
@@ -17121,6 +17590,7 @@
       <c r="I538" t="n">
         <v>377.7072913135326</v>
       </c>
+      <c r="J538" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" t="n">
@@ -17152,6 +17622,7 @@
       <c r="I539" t="n">
         <v>380.8272745277539</v>
       </c>
+      <c r="J539" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" t="n">
@@ -17183,6 +17654,7 @@
       <c r="I540" t="n">
         <v>383.7763030349461</v>
       </c>
+      <c r="J540" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" t="n">
@@ -17214,6 +17686,7 @@
       <c r="I541" t="n">
         <v>393.0334756174935</v>
       </c>
+      <c r="J541" t="inlineStr"/>
     </row>
     <row r="542">
       <c r="A542" t="n">
@@ -17245,6 +17718,7 @@
       <c r="I542" t="n">
         <v>381.8569587182603</v>
       </c>
+      <c r="J542" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" t="n">
@@ -17276,6 +17750,7 @@
       <c r="I543" t="n">
         <v>376.1480619672212</v>
       </c>
+      <c r="J543" t="inlineStr"/>
     </row>
     <row r="544">
       <c r="A544" t="n">
@@ -17307,6 +17782,7 @@
       <c r="I544" t="n">
         <v>377.3502885409321</v>
       </c>
+      <c r="J544" t="inlineStr"/>
     </row>
     <row r="545">
       <c r="A545" t="n">
@@ -17338,6 +17814,7 @@
       <c r="I545" t="n">
         <v>376.407689028033</v>
       </c>
+      <c r="J545" t="inlineStr"/>
     </row>
     <row r="546">
       <c r="A546" t="n">
@@ -17369,6 +17846,7 @@
       <c r="I546" t="n">
         <v>377.7072913135326</v>
       </c>
+      <c r="J546" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" t="n">
@@ -17400,6 +17878,7 @@
       <c r="I547" t="n">
         <v>391.4732273066421</v>
       </c>
+      <c r="J547" t="inlineStr"/>
     </row>
     <row r="548">
       <c r="A548" t="n">
@@ -17431,6 +17910,7 @@
       <c r="I548" t="n">
         <v>425.1370443293342</v>
       </c>
+      <c r="J548" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" t="n">
@@ -17462,6 +17942,7 @@
       <c r="I549" t="n">
         <v>376.1480619672212</v>
       </c>
+      <c r="J549" t="inlineStr"/>
     </row>
     <row r="550">
       <c r="A550" t="n">
@@ -17491,8 +17972,9 @@
         <v>369.4336570186837</v>
       </c>
       <c r="I550" t="n">
-        <v>376.4076890280331</v>
-      </c>
+        <v>376.407689028033</v>
+      </c>
+      <c r="J550" t="inlineStr"/>
     </row>
     <row r="551">
       <c r="A551" t="n">
@@ -17524,6 +18006,7 @@
       <c r="I551" t="n">
         <v>377.7072913135326</v>
       </c>
+      <c r="J551" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
